--- a/数据表/Datas/EnemyDropConfig_敌人掉落配置.xlsx
+++ b/数据表/Datas/EnemyDropConfig_敌人掉落配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -35,19 +40,13 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>*lootConfigs</t>
   </si>
   <si>
     <t>##type</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
+    <t>EnemyPartyThreatLevel</t>
   </si>
   <si>
     <t>list,LootGenerationConfig</t>
@@ -84,56 +83,107 @@
   </si>
   <si>
     <t>##</t>
+  </si>
+  <si>
+    <t>威胁等级ID</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Carlito"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>掉落表</t>
+      <t>难度档位</t>
     </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>ID</t>
+      <t>最少生成数量</t>
     </r>
   </si>
   <si>
-    <t>显示名</t>
-  </si>
-  <si>
-    <t>难度档位</t>
-  </si>
-  <si>
-    <t>最少生成数量</t>
-  </si>
-  <si>
-    <t>最多生成数量</t>
-  </si>
-  <si>
-    <t>白色权重</t>
-  </si>
-  <si>
-    <t>绿色权重</t>
-  </si>
-  <si>
-    <t>蓝色权重</t>
-  </si>
-  <si>
-    <t>金色权重</t>
-  </si>
-  <si>
-    <t>红色权重</t>
-  </si>
-  <si>
-    <t>普通敌人掉落</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最多生成数量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>白色权重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>绿色权重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蓝色权重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>金色权重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>红色权重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低</t>
+    </r>
   </si>
   <si>
     <t>Tier1</t>
@@ -145,10 +195,24 @@
     <t>Tier3</t>
   </si>
   <si>
-    <t>中级敌人掉落</t>
-  </si>
-  <si>
-    <t>高级敌人掉落</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -169,49 +233,43 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Carlito"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="Carlito"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -364,6 +422,11 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -845,153 +908,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1042,13 +1105,16 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1522,449 +1588,418 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.7058823529412" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.8088235294118" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.4558823529412" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.4705882352941" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.9117647058824" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.3161764705882" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.3529411764706" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.4558823529412" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.1985294117647" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="2" max="2" width="27.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.8083333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.4583333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.4666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.9083333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.3166666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.35" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.4583333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.2" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
+    <row r="1" customHeight="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
+      <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
+      <c r="J1" s="7"/>
     </row>
-    <row r="2" customHeight="1" spans="1:11">
+    <row r="2" customHeight="1" spans="1:10">
       <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="12"/>
+      <c r="J2" s="12"/>
     </row>
-    <row r="3" customHeight="1" spans="1:11">
+    <row r="3" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>7</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:11">
+    <row r="4" customHeight="1" spans="1:10">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="4" t="s">
+    </row>
+    <row r="5" customHeight="1" spans="1:10">
+      <c r="A5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
+      <c r="C5" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="17" t="s">
+    <row r="6" customHeight="1" spans="1:10">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="C6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:11">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19">
+      <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>30</v>
-      </c>
       <c r="E6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
+        <v>85</v>
+      </c>
+      <c r="G6" s="2">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2">
         <v>2</v>
       </c>
-      <c r="G6" s="2">
-        <v>85</v>
-      </c>
-      <c r="H6" s="2">
-        <v>13</v>
-      </c>
       <c r="I6" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
       </c>
-      <c r="K6" s="2">
+    </row>
+    <row r="7" customHeight="1" spans="1:10">
+      <c r="A7" s="19"/>
+      <c r="C7" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>65</v>
+      </c>
+      <c r="G7" s="2">
+        <v>25</v>
+      </c>
+      <c r="H7" s="2">
+        <v>8</v>
+      </c>
+      <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:11">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="19" t="s">
+    <row r="8" customHeight="1" spans="1:10">
+      <c r="A8" s="19"/>
+      <c r="C8" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>45</v>
+      </c>
+      <c r="G8" s="2">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8</v>
+      </c>
+      <c r="J8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:10">
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:10">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>65</v>
+      </c>
+      <c r="G10" s="2">
+        <v>25</v>
+      </c>
+      <c r="H10" s="2">
+        <v>8</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:10">
+      <c r="A11" s="19"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>45</v>
+      </c>
+      <c r="G11" s="2">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2">
+        <v>18</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
+      <c r="A12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>25</v>
+      </c>
+      <c r="G12" s="2">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2">
+        <v>25</v>
+      </c>
+      <c r="I12" s="2">
+        <v>15</v>
+      </c>
+      <c r="J12" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
+      <c r="A13" s="19"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
+      <c r="A14" s="19"/>
+      <c r="B14" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="2">
+      <c r="C14" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="F7" s="2">
+      <c r="E14" s="2">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>45</v>
+      </c>
+      <c r="G14" s="2">
+        <v>35</v>
+      </c>
+      <c r="H14" s="2">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:10">
+      <c r="C15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>25</v>
+      </c>
+      <c r="G15" s="2">
+        <v>35</v>
+      </c>
+      <c r="H15" s="2">
+        <v>25</v>
+      </c>
+      <c r="I15" s="2">
+        <v>12</v>
+      </c>
+      <c r="J15" s="2">
         <v>3</v>
       </c>
-      <c r="G7" s="2">
-        <v>65</v>
-      </c>
-      <c r="H7" s="2">
+    </row>
+    <row r="16" customHeight="1" spans="1:10">
+      <c r="C16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2">
         <v>25</v>
       </c>
-      <c r="I7" s="2">
-        <v>8</v>
-      </c>
-      <c r="J7" s="2">
-        <v>2</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:11">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="2">
-        <v>2</v>
-      </c>
-      <c r="F8" s="2">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2">
-        <v>45</v>
-      </c>
-      <c r="H8" s="2">
+      <c r="H16" s="2">
         <v>30</v>
       </c>
-      <c r="I8" s="2">
-        <v>15</v>
-      </c>
-      <c r="J8" s="2">
-        <v>8</v>
-      </c>
-      <c r="K8" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:11">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="19"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:11">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19">
-        <v>2</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
-        <v>65</v>
-      </c>
-      <c r="H10" s="2">
+      <c r="I16" s="2">
         <v>25</v>
       </c>
-      <c r="I10" s="2">
-        <v>8</v>
-      </c>
-      <c r="J10" s="2">
-        <v>2</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:11">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2</v>
-      </c>
-      <c r="G11" s="2">
-        <v>45</v>
-      </c>
-      <c r="H11" s="2">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2">
-        <v>18</v>
-      </c>
-      <c r="J11" s="2">
-        <v>6</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:11">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2">
-        <v>2</v>
-      </c>
-      <c r="G12" s="2">
-        <v>25</v>
-      </c>
-      <c r="H12" s="2">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2">
-        <v>25</v>
-      </c>
-      <c r="J12" s="2">
-        <v>15</v>
-      </c>
-      <c r="K12" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:11">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="19"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:11">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19">
-        <v>3</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2">
-        <v>2</v>
-      </c>
-      <c r="G14" s="2">
-        <v>45</v>
-      </c>
-      <c r="H14" s="2">
-        <v>35</v>
-      </c>
-      <c r="I14" s="2">
-        <v>15</v>
-      </c>
-      <c r="J14" s="2">
-        <v>5</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:11">
-      <c r="D15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2">
-        <v>2</v>
-      </c>
-      <c r="G15" s="2">
-        <v>25</v>
-      </c>
-      <c r="H15" s="2">
-        <v>35</v>
-      </c>
-      <c r="I15" s="2">
-        <v>25</v>
-      </c>
-      <c r="J15" s="2">
-        <v>12</v>
-      </c>
-      <c r="K15" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:11">
-      <c r="D16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
-        <v>3</v>
-      </c>
-      <c r="G16" s="2">
-        <v>10</v>
-      </c>
-      <c r="H16" s="2">
-        <v>25</v>
-      </c>
-      <c r="I16" s="2">
-        <v>30</v>
-      </c>
       <c r="J16" s="2">
-        <v>25</v>
-      </c>
-      <c r="K16" s="2">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="D1:K1"/>
-    <mergeCell ref="D2:K2"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="C2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
